--- a/reports/pro-crypto/pro-crypto-refunds-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-refunds-report.xlsx
@@ -36,27 +36,6 @@
   </x:si>
   <x:si>
     <x:t>refund_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>C00887356</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REPUBLICANS FOR A PRO-CRYPTO SENATE MAJORITY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00819888</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUTY FIRST PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00850610</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MR PAC</x:t>
   </x:si>
   <x:si>
     <x:t>HILL, JAMES FRENCH</x:t>
@@ -161,8 +140,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G4" totalsRowShown="0">
-  <x:autoFilter ref="A1:G4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G2" totalsRowShown="0">
+  <x:autoFilter ref="A1:G2"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -177,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H4" totalsRowShown="0">
-  <x:autoFilter ref="A1:H4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H2" totalsRowShown="0">
+  <x:autoFilter ref="A1:H2"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -481,7 +460,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G4"/>
+  <x:dimension ref="A1:G2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -534,55 +513,9 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>-1526</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G2" s="2">
-        <x:v>45600</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="1">
-        <x:v>-1525</x:v>
-      </x:c>
-      <x:c r="G3" s="2">
-        <x:v>45600</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F4" s="1">
-        <x:v>-2500</x:v>
-      </x:c>
-      <x:c r="G4" s="2">
         <x:v>45631</x:v>
       </x:c>
     </x:row>
@@ -602,7 +535,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H4"/>
+  <x:dimension ref="A1:H2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -633,13 +566,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -659,64 +592,12 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>-1526</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>11576</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
-      <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="1">
-        <x:v>-1525</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="1">
-        <x:v>13356</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F4" s="1">
-        <x:v>-2500</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H4" s="1">
         <x:v>1500</x:v>
       </x:c>
     </x:row>
